--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -964,14 +964,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="16">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="16">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -687,7 +687,7 @@
     <t>10001</t>
   </si>
   <si>
-    <t>-1546,0,610</t>
+    <t>-216,0,610</t>
   </si>
   <si>
     <t>路过邮箱时看到有几封信叠着，阳光映出轮廓，像极了你等的那封！快去看看是不是到啦。</t>
@@ -696,19 +696,19 @@
     <t>巧儿</t>
   </si>
   <si>
-    <t>-2334,0,625</t>
+    <t>311,0,-625</t>
   </si>
   <si>
     <t>鉴定家</t>
   </si>
   <si>
-    <t>-2353,0,-429</t>
+    <t>657,0,-401</t>
   </si>
   <si>
     <t>珠宝匠</t>
   </si>
   <si>
-    <t>2513,0,-1741</t>
+    <t>795,0,-36</t>
   </si>
   <si>
     <t>你这么有爱心，养只宠物的话肯定会很幸福呀，有没有考虑过呀？</t>
@@ -717,13 +717,13 @@
     <t>锻造师</t>
   </si>
   <si>
-    <t>-1160,134,610</t>
+    <t>704,0,306</t>
   </si>
   <si>
     <t>合成师</t>
   </si>
   <si>
-    <t>-719,0,-444</t>
+    <t>404,0,515</t>
   </si>
   <si>
     <t>铸剑山庄学徒</t>
@@ -732,13 +732,13 @@
     <t>0</t>
   </si>
   <si>
-    <t>-1565,128,-444</t>
+    <t>-93,0,557</t>
   </si>
   <si>
     <t>裁缝</t>
   </si>
   <si>
-    <t>-1179,0,-444</t>
+    <t>-467,0,359</t>
   </si>
   <si>
     <t>在这里接取超有趣的任务，海量金币奖励直接抱回家～解锁任务成就，让金币“叮叮当”装满你的小金库吧！</t>
@@ -747,7 +747,7 @@
     <t>红娘</t>
   </si>
   <si>
-    <t>-700,0,610</t>
+    <t>-571,0,43</t>
   </si>
   <si>
     <t>传说这里有只守护巨兽，击败它能拿丰厚奖励！</t>
@@ -756,7 +756,7 @@
     <t>武馆教头</t>
   </si>
   <si>
-    <t>5235,0,-2423</t>
+    <t>-572,0,-307</t>
   </si>
 </sst>
 </file>
@@ -958,17 +958,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -976,7 +976,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -958,8 +958,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -969,14 +975,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="16">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H8" s="16">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22110" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="16">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H9" s="16">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="16">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="H10" s="16">
         <v>0</v>
